--- a/other/riverfocus_deliverables/CombinedData_11082024.xlsx
+++ b/other/riverfocus_deliverables/CombinedData_11082024.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bd0dd052dcf49e10/Documents/GitHub_Local/fish-passage-prioritization/other/riverfocus_deliverables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmeyer\Documents\github_local\fish-passage-prioritization\other\riverfocus_deliverables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_57BCF82BA21A2D8E32E58329E51CE5F9DE05151D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE60FD64-F8CC-4A9A-A30A-1A91B9439118}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="24405" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="24408" windowHeight="11292"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -1744,7 +1743,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2074,11 +2073,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB420"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2164,7 +2163,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>60.801796000000003</v>
       </c>
@@ -2193,7 +2192,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>60.530790000000003</v>
       </c>
@@ -2225,7 +2224,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>60.438609999999997</v>
       </c>
@@ -2254,7 +2253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>60.066704000000001</v>
       </c>
@@ -2280,7 +2279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>60.312283000000001</v>
       </c>
@@ -2306,7 +2305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>60.027645</v>
       </c>
@@ -2332,7 +2331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>59.800364999999999</v>
       </c>
@@ -2361,7 +2360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>60.526260000000001</v>
       </c>
@@ -2387,7 +2386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>60.009284999999998</v>
       </c>
@@ -2413,7 +2412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>60.858789999999999</v>
       </c>
@@ -2442,7 +2441,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>60.703099999999999</v>
       </c>
@@ -2471,7 +2470,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>60.704177999999999</v>
       </c>
@@ -2500,7 +2499,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>60.071067999999997</v>
       </c>
@@ -2526,7 +2525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>60.744883999999999</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>60.800229999999999</v>
       </c>
@@ -2584,7 +2583,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>60.020499999999998</v>
       </c>
@@ -2610,7 +2609,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>60.811348000000002</v>
       </c>
@@ -2639,7 +2638,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>60.781179999999999</v>
       </c>
@@ -2677,7 +2676,7 @@
         <v>48.11</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>59.773737390000001</v>
       </c>
@@ -2712,7 +2711,7 @@
         <v>137.02000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>60.355170110000003</v>
       </c>
@@ -2750,7 +2749,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>59.800448330000002</v>
       </c>
@@ -2785,7 +2784,7 @@
         <v>36.950000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>60.594681289999997</v>
       </c>
@@ -2820,7 +2819,7 @@
         <v>25.09</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>60.483611230000001</v>
       </c>
@@ -2858,7 +2857,7 @@
         <v>11.09</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>60.778852489999998</v>
       </c>
@@ -2890,7 +2889,7 @@
         <v>22.39</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>59.756636970000002</v>
       </c>
@@ -2925,7 +2924,7 @@
         <v>21.08</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>60.563270039999999</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>41.09</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>60.670256729999998</v>
       </c>
@@ -2995,7 +2994,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>59.991036180000002</v>
       </c>
@@ -3033,7 +3032,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>60.9187297</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>15.12</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>59.669146820000002</v>
       </c>
@@ -3100,7 +3099,7 @@
         <v>15.21</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>59.7085644</v>
       </c>
@@ -3132,7 +3131,7 @@
         <v>30.41</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>60.190586320000001</v>
       </c>
@@ -3164,7 +3163,7 @@
         <v>14.09</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>60.436494000000003</v>
       </c>
@@ -3196,7 +3195,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>60.049904589999997</v>
       </c>
@@ -3234,7 +3233,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>60.724875930000003</v>
       </c>
@@ -3266,7 +3265,7 @@
         <v>11.31</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>60.497979260000001</v>
       </c>
@@ -3301,7 +3300,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>59.441310000000001</v>
       </c>
@@ -3339,7 +3338,7 @@
         <v>8.4700000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>60.171705340000003</v>
       </c>
@@ -3371,7 +3370,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>60.50160588</v>
       </c>
@@ -3406,7 +3405,7 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>60.204350660000003</v>
       </c>
@@ -3441,7 +3440,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>60.46997022</v>
       </c>
@@ -3476,7 +3475,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>59.66386061</v>
       </c>
@@ -3511,7 +3510,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>60.182771340000002</v>
       </c>
@@ -3546,7 +3545,7 @@
         <v>10.79</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>60.123440000000002</v>
       </c>
@@ -3581,7 +3580,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>59.953012700000002</v>
       </c>
@@ -3613,7 +3612,7 @@
         <v>10.91</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>60.525000640000002</v>
       </c>
@@ -3648,7 +3647,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>60.504696000000003</v>
       </c>
@@ -3686,7 +3685,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>59.712260000000001</v>
       </c>
@@ -3718,7 +3717,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>60.473268390000001</v>
       </c>
@@ -3753,7 +3752,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>60.465286999999996</v>
       </c>
@@ -3791,7 +3790,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>60.740107420000001</v>
       </c>
@@ -3829,7 +3828,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>60.233518089999997</v>
       </c>
@@ -3861,7 +3860,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>60.558046589999996</v>
       </c>
@@ -3893,7 +3892,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>60.643254689999999</v>
       </c>
@@ -3925,7 +3924,7 @@
         <v>9.11</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>59.744646940000003</v>
       </c>
@@ -3960,7 +3959,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>60.530731979999999</v>
       </c>
@@ -3995,7 +3994,7 @@
         <v>7.72</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>60.801405680000002</v>
       </c>
@@ -4027,7 +4026,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>60.750893490000003</v>
       </c>
@@ -4059,7 +4058,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59.936921249999997</v>
       </c>
@@ -4091,7 +4090,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60.049432320000001</v>
       </c>
@@ -4126,7 +4125,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>60.610120000000002</v>
       </c>
@@ -4158,7 +4157,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>60.70577565</v>
       </c>
@@ -4193,7 +4192,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>60.559728</v>
       </c>
@@ -4228,7 +4227,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>60.455620799999998</v>
       </c>
@@ -4263,7 +4262,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>60.310449570000003</v>
       </c>
@@ -4295,7 +4294,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>60.493131200000001</v>
       </c>
@@ -4330,7 +4329,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>60.056860780000001</v>
       </c>
@@ -4365,7 +4364,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>59.870993839999997</v>
       </c>
@@ -4403,7 +4402,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>60.066706699999997</v>
       </c>
@@ -4438,7 +4437,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>60.537459660000003</v>
       </c>
@@ -4473,7 +4472,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>59.881048380000003</v>
       </c>
@@ -4511,7 +4510,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>60.486980000000003</v>
       </c>
@@ -4546,7 +4545,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>60.027508240000003</v>
       </c>
@@ -4581,7 +4580,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>59.994576780000003</v>
       </c>
@@ -4616,7 +4615,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>60.00979873</v>
       </c>
@@ -4651,7 +4650,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>60.793725999999999</v>
       </c>
@@ -4686,7 +4685,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>59.292914619999998</v>
       </c>
@@ -4721,7 +4720,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>60.542389999999997</v>
       </c>
@@ -4756,7 +4755,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>60.7897119</v>
       </c>
@@ -4791,7 +4790,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>60.509169999999997</v>
       </c>
@@ -4829,7 +4828,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>60.741502699999998</v>
       </c>
@@ -4861,7 +4860,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>60.441870489999999</v>
       </c>
@@ -4893,7 +4892,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>59.983881340000003</v>
       </c>
@@ -4928,7 +4927,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>60.5090273</v>
       </c>
@@ -4963,7 +4962,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>60.513574009999999</v>
       </c>
@@ -4995,7 +4994,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>60.560026000000001</v>
       </c>
@@ -5033,7 +5032,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>59.289850379999997</v>
       </c>
@@ -5068,7 +5067,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>59.766377650000003</v>
       </c>
@@ -5100,7 +5099,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>59.310872369999998</v>
       </c>
@@ -5135,7 +5134,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>60.539499999999997</v>
       </c>
@@ -5170,7 +5169,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>59.24984594</v>
       </c>
@@ -5202,7 +5201,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>60.731911750000002</v>
       </c>
@@ -5234,7 +5233,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>59.818449770000001</v>
       </c>
@@ -5266,7 +5265,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>60.53529881</v>
       </c>
@@ -5301,7 +5300,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>60.184915109999999</v>
       </c>
@@ -5336,7 +5335,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>60.512276</v>
       </c>
@@ -5371,7 +5370,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>60.5575191</v>
       </c>
@@ -5409,7 +5408,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>59.302434349999999</v>
       </c>
@@ -5447,7 +5446,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>60.122529399999998</v>
       </c>
@@ -5482,7 +5481,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>60.140394550000003</v>
       </c>
@@ -5514,7 +5513,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>60.51814177</v>
       </c>
@@ -5549,7 +5548,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>60.089469999999999</v>
       </c>
@@ -5581,7 +5580,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>60.55965904</v>
       </c>
@@ -5616,7 +5615,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>60.551057180000001</v>
       </c>
@@ -5651,7 +5650,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>60.513101030000001</v>
       </c>
@@ -5686,7 +5685,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>60.549259999999997</v>
       </c>
@@ -5718,7 +5717,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>60.513401000000002</v>
       </c>
@@ -5750,7 +5749,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>60.120980000000003</v>
       </c>
@@ -5785,7 +5784,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>60.48345123</v>
       </c>
@@ -5817,7 +5816,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>60.045752610000001</v>
       </c>
@@ -5849,7 +5848,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>60.114310000000003</v>
       </c>
@@ -5881,7 +5880,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>60.112470000000002</v>
       </c>
@@ -5913,7 +5912,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>60.11215</v>
       </c>
@@ -5945,7 +5944,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>60.191417000000001</v>
       </c>
@@ -5977,7 +5976,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>60.155048000000001</v>
       </c>
@@ -6009,7 +6008,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>60.155189999999997</v>
       </c>
@@ -6041,7 +6040,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>60.155209999999997</v>
       </c>
@@ -6073,7 +6072,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>59.307661699999997</v>
       </c>
@@ -6105,7 +6104,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>59.297712330000003</v>
       </c>
@@ -6137,7 +6136,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>59.302139140000001</v>
       </c>
@@ -6169,7 +6168,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>60.524287999999999</v>
       </c>
@@ -6204,7 +6203,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>60.510582999999997</v>
       </c>
@@ -6236,7 +6235,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>60.439680469999999</v>
       </c>
@@ -6271,7 +6270,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>60.154310000000002</v>
       </c>
@@ -6306,7 +6305,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>60.547280000000001</v>
       </c>
@@ -6341,7 +6340,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>60.12032</v>
       </c>
@@ -6376,7 +6375,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>60.74939002</v>
       </c>
@@ -6408,7 +6407,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>60.154980000000002</v>
       </c>
@@ -6440,7 +6439,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>60.151220000000002</v>
       </c>
@@ -6472,7 +6471,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>59.301747820000003</v>
       </c>
@@ -6504,7 +6503,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>60.042189860000001</v>
       </c>
@@ -6536,7 +6535,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>60.546750000000003</v>
       </c>
@@ -6568,7 +6567,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>60.165919459999998</v>
       </c>
@@ -6600,7 +6599,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>60.52403537</v>
       </c>
@@ -6632,7 +6631,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>60.537409660000002</v>
       </c>
@@ -6664,7 +6663,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>60.242001180000003</v>
       </c>
@@ -6696,7 +6695,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>59.30850014</v>
       </c>
@@ -6728,7 +6727,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>60.487869979999999</v>
       </c>
@@ -6760,7 +6759,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>59.800987859999999</v>
       </c>
@@ -6792,7 +6791,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>60.124489359999998</v>
       </c>
@@ -6824,7 +6823,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>60.113750000000003</v>
       </c>
@@ -6853,7 +6852,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>60.113149</v>
       </c>
@@ -6882,7 +6881,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>60.112839999999998</v>
       </c>
@@ -6911,7 +6910,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>60.112659999999998</v>
       </c>
@@ -6940,7 +6939,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>60.148969999999998</v>
       </c>
@@ -6969,7 +6968,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>59.308133890000001</v>
       </c>
@@ -6998,7 +6997,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>59.296714350000002</v>
       </c>
@@ -7027,7 +7026,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>60.730924590000001</v>
       </c>
@@ -7056,7 +7055,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>60.823613100000003</v>
       </c>
@@ -7085,7 +7084,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>59.46002</v>
       </c>
@@ -7117,7 +7116,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>59.452350000000003</v>
       </c>
@@ -7149,7 +7148,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>60.113410000000002</v>
       </c>
@@ -7178,7 +7177,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>59.330905940000001</v>
       </c>
@@ -7207,7 +7206,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>59.278548700000002</v>
       </c>
@@ -7236,7 +7235,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>60.743308249999998</v>
       </c>
@@ -7265,7 +7264,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>60.744908649999999</v>
       </c>
@@ -7294,7 +7293,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>60.727771570000002</v>
       </c>
@@ -7323,7 +7322,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>60.524092029999998</v>
       </c>
@@ -7352,7 +7351,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>59.447719999999997</v>
       </c>
@@ -7381,7 +7380,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>60.524317000000003</v>
       </c>
@@ -7410,7 +7409,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>59.712200000000003</v>
       </c>
@@ -7439,7 +7438,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>60.14376</v>
       </c>
@@ -7474,7 +7473,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>60.167479999999998</v>
       </c>
@@ -7509,7 +7508,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>60.113349999999997</v>
       </c>
@@ -7538,7 +7537,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>60.16084</v>
       </c>
@@ -7573,7 +7572,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>60.119669999999999</v>
       </c>
@@ -7608,7 +7607,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>60.155340000000002</v>
       </c>
@@ -7637,7 +7636,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>60.129013999999998</v>
       </c>
@@ -7669,7 +7668,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>60.132559999999998</v>
       </c>
@@ -7698,7 +7697,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>60.130530999999998</v>
       </c>
@@ -7730,7 +7729,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>60.128596000000002</v>
       </c>
@@ -7762,7 +7761,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>60.127526000000003</v>
       </c>
@@ -7794,7 +7793,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>60.16718985</v>
       </c>
@@ -7823,7 +7822,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>60.151418759999999</v>
       </c>
@@ -7855,7 +7854,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>60.027286680000003</v>
       </c>
@@ -7890,7 +7889,7 @@
         <v>25.09</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>60.049266160000002</v>
       </c>
@@ -7925,7 +7924,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>60.07111647</v>
       </c>
@@ -7960,7 +7959,7 @@
         <v>12.13</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>60.126710789999997</v>
       </c>
@@ -7992,7 +7991,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>59.953736749999997</v>
       </c>
@@ -8021,7 +8020,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>59.985105480000001</v>
       </c>
@@ -8053,7 +8052,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>59.992411799999999</v>
       </c>
@@ -8085,7 +8084,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>60.050307619999998</v>
       </c>
@@ -8117,7 +8116,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>60.064656370000002</v>
       </c>
@@ -8152,7 +8151,7 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>59.334796750000002</v>
       </c>
@@ -8181,7 +8180,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>59.325995370000001</v>
       </c>
@@ -8210,7 +8209,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>59.320247799999997</v>
       </c>
@@ -8242,7 +8241,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>59.303690570000001</v>
       </c>
@@ -8277,7 +8276,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>59.306078720000002</v>
       </c>
@@ -8312,7 +8311,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>59.343013419999998</v>
       </c>
@@ -8341,7 +8340,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>59.28940489</v>
       </c>
@@ -8370,7 +8369,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>59.278688260000003</v>
       </c>
@@ -8399,7 +8398,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>60.493134400000002</v>
       </c>
@@ -8434,7 +8433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>60.524105579999997</v>
       </c>
@@ -8463,7 +8462,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>60.599440250000001</v>
       </c>
@@ -8495,7 +8494,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>60.817388520000002</v>
       </c>
@@ -8527,7 +8526,7 @@
         <v>8.27</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>60.476408470000003</v>
       </c>
@@ -8562,7 +8561,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>60.433438199999998</v>
       </c>
@@ -8597,7 +8596,7 @@
         <v>24.42</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>60.350830000000002</v>
       </c>
@@ -8632,7 +8631,7 @@
         <v>47.94</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>60.775076480000003</v>
       </c>
@@ -8664,7 +8663,7 @@
         <v>47.13</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>60.567290079999999</v>
       </c>
@@ -8696,7 +8695,7 @@
         <v>9.31</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>60.302050970000003</v>
       </c>
@@ -8731,7 +8730,7 @@
         <v>123.93</v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>59.851436329999999</v>
       </c>
@@ -8766,7 +8765,7 @@
         <v>134.96</v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>59.713859999999997</v>
       </c>
@@ -8801,7 +8800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>60.516648240000002</v>
       </c>
@@ -8836,7 +8835,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>60.517608240000001</v>
       </c>
@@ -8871,7 +8870,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>60.487759109999999</v>
       </c>
@@ -8906,7 +8905,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>60.457845059999997</v>
       </c>
@@ -8941,7 +8940,7 @@
         <v>11.36</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>60.731486750000002</v>
       </c>
@@ -8973,7 +8972,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>60.54427913</v>
       </c>
@@ -9008,7 +9007,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>60.704065559999997</v>
       </c>
@@ -9043,7 +9042,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>60.704105749999997</v>
       </c>
@@ -9078,7 +9077,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>60.70315566</v>
       </c>
@@ -9110,7 +9109,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>60.507320970000002</v>
       </c>
@@ -9145,7 +9144,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>59.738280000000003</v>
       </c>
@@ -9180,7 +9179,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>60.010663280000003</v>
       </c>
@@ -9215,7 +9214,7 @@
         <v>45.39</v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>60.296370879999998</v>
       </c>
@@ -9244,7 +9243,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>60.513390000000001</v>
       </c>
@@ -9279,7 +9278,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>60.728940000000001</v>
       </c>
@@ -9314,7 +9313,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>59.444740000000003</v>
       </c>
@@ -9343,7 +9342,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>59.452350000000003</v>
       </c>
@@ -9375,7 +9374,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>59.476439999999997</v>
       </c>
@@ -9404,7 +9403,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>59.476619999999997</v>
       </c>
@@ -9433,7 +9432,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>59.478180000000002</v>
       </c>
@@ -9462,7 +9461,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>59.464709999999997</v>
       </c>
@@ -9494,7 +9493,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>59.438000000000002</v>
       </c>
@@ -9523,7 +9522,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>60.567283000000003</v>
       </c>
@@ -9558,7 +9557,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>60.56127</v>
       </c>
@@ -9593,7 +9592,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>60.527700000000003</v>
       </c>
@@ -9628,7 +9627,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>60.502797000000001</v>
       </c>
@@ -9663,7 +9662,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>60.545569</v>
       </c>
@@ -9695,7 +9694,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>60.547584000000001</v>
       </c>
@@ -9727,7 +9726,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>60.689300000000003</v>
       </c>
@@ -9762,7 +9761,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>60.717007000000002</v>
       </c>
@@ -9794,7 +9793,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>60.690415999999999</v>
       </c>
@@ -9829,7 +9828,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>60.565187000000002</v>
       </c>
@@ -9864,7 +9863,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>60.561208000000001</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>60.560129000000003</v>
       </c>
@@ -9931,7 +9930,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>60.516095</v>
       </c>
@@ -9963,7 +9962,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>60.513741000000003</v>
       </c>
@@ -9998,7 +9997,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="241" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>60.495381000000002</v>
       </c>
@@ -10033,7 +10032,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="242" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>60.487490000000001</v>
       </c>
@@ -10068,7 +10067,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="243" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>60.489598999999998</v>
       </c>
@@ -10100,7 +10099,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="244" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>60.533335000000001</v>
       </c>
@@ -10132,7 +10131,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="245" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>60.524366999999998</v>
       </c>
@@ -10164,7 +10163,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="246" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>60.273352000000003</v>
       </c>
@@ -10199,7 +10198,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="247" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>60.275027000000001</v>
       </c>
@@ -10231,7 +10230,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="248" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>60.291739999999997</v>
       </c>
@@ -10266,7 +10265,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="249" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>60.534388999999997</v>
       </c>
@@ -10295,7 +10294,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="250" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>60.533290000000001</v>
       </c>
@@ -10324,7 +10323,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="251" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>60.524909999999998</v>
       </c>
@@ -10359,7 +10358,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="252" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>60.294759999999997</v>
       </c>
@@ -10394,7 +10393,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="253" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>60.302346</v>
       </c>
@@ -10423,7 +10422,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="254" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>60.621000000000002</v>
       </c>
@@ -10452,7 +10451,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="255" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>60.543835000000001</v>
       </c>
@@ -10496,7 +10495,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="256" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>60.551447000000003</v>
       </c>
@@ -10543,7 +10542,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="257" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>60.502809999999997</v>
       </c>
@@ -10581,7 +10580,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="258" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>60.302067999999998</v>
       </c>
@@ -10625,7 +10624,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="259" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>60.263697999999998</v>
       </c>
@@ -10669,7 +10668,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="260" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>60.436549999999997</v>
       </c>
@@ -10713,7 +10712,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="261" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>60.433362000000002</v>
       </c>
@@ -10757,7 +10756,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="262" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>60.473182999999999</v>
       </c>
@@ -10801,7 +10800,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="263" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>60.516649999999998</v>
       </c>
@@ -10845,7 +10844,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="264" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>60.473444999999998</v>
       </c>
@@ -10892,7 +10891,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="265" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>60.473660000000002</v>
       </c>
@@ -10939,7 +10938,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="266" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>60.567202000000002</v>
       </c>
@@ -10983,7 +10982,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="267" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>60.560014000000002</v>
       </c>
@@ -11027,7 +11026,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="268" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>60.476525000000002</v>
       </c>
@@ -11071,7 +11070,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="269" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>60.513379</v>
       </c>
@@ -11115,7 +11114,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="270" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>60.518084000000002</v>
       </c>
@@ -11159,7 +11158,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="271" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>60.529623000000001</v>
       </c>
@@ -11203,7 +11202,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="272" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>60.528432000000002</v>
       </c>
@@ -11247,7 +11246,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="273" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>60.550871999999998</v>
       </c>
@@ -11291,7 +11290,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="274" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>60.552858999999998</v>
       </c>
@@ -11335,7 +11334,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="275" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>60.544732000000003</v>
       </c>
@@ -11379,7 +11378,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="276" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>60.544178000000002</v>
       </c>
@@ -11423,7 +11422,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="277" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>60.560132000000003</v>
       </c>
@@ -11464,7 +11463,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="278" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>60.558625999999997</v>
       </c>
@@ -11508,7 +11507,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="279" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>60.559897999999997</v>
       </c>
@@ -11552,7 +11551,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="280" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>60.539445999999998</v>
       </c>
@@ -11596,7 +11595,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="281" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>60.547573</v>
       </c>
@@ -11634,7 +11633,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="282" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>60.541946000000003</v>
       </c>
@@ -11675,7 +11674,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="283" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>60.547286</v>
       </c>
@@ -11719,7 +11718,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="284" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>60.010714</v>
       </c>
@@ -11763,7 +11762,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="285" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>59.889726000000003</v>
       </c>
@@ -11804,7 +11803,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="286" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>60.009824999999999</v>
       </c>
@@ -11845,7 +11844,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="287" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>59.990980999999998</v>
       </c>
@@ -11892,7 +11891,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="288" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>59.889726000000003</v>
       </c>
@@ -11936,7 +11935,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="289" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>59.899141999999998</v>
       </c>
@@ -11983,7 +11982,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="290" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>59.903934999999997</v>
       </c>
@@ -12027,7 +12026,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="291" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>59.895373999999997</v>
       </c>
@@ -12071,7 +12070,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="292" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>59.796548999999999</v>
       </c>
@@ -12115,7 +12114,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="293" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>59.993304000000002</v>
       </c>
@@ -12162,7 +12161,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="294" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>60.557586999999998</v>
       </c>
@@ -12203,7 +12202,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="295" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>60.775564000000003</v>
       </c>
@@ -12247,7 +12246,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="296" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>59.794373</v>
       </c>
@@ -12291,7 +12290,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="297" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>59.803417000000003</v>
       </c>
@@ -12335,7 +12334,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="298" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>59.800241999999997</v>
       </c>
@@ -12379,7 +12378,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="299" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>59.791307000000003</v>
       </c>
@@ -12423,7 +12422,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="300" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>59.712266999999997</v>
       </c>
@@ -12467,7 +12466,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="301" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>60.543835000000001</v>
       </c>
@@ -12508,7 +12507,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="302" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>60.551447000000003</v>
       </c>
@@ -12552,7 +12551,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="303" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>60.502809999999997</v>
       </c>
@@ -12587,7 +12586,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="304" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>60.302067999999998</v>
       </c>
@@ -12628,7 +12627,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="305" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>60.263697999999998</v>
       </c>
@@ -12669,7 +12668,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="306" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>60.436549999999997</v>
       </c>
@@ -12710,7 +12709,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="307" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>60.433362000000002</v>
       </c>
@@ -12751,7 +12750,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="308" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>60.473182999999999</v>
       </c>
@@ -12792,7 +12791,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="309" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>60.516649999999998</v>
       </c>
@@ -12833,7 +12832,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="310" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>60.473444999999998</v>
       </c>
@@ -12877,7 +12876,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="311" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>60.473660000000002</v>
       </c>
@@ -12921,7 +12920,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="312" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>60.567202000000002</v>
       </c>
@@ -12962,7 +12961,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="313" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>60.560014000000002</v>
       </c>
@@ -13003,7 +13002,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="314" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>60.476525000000002</v>
       </c>
@@ -13044,7 +13043,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="315" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>60.513379</v>
       </c>
@@ -13085,7 +13084,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="316" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>60.518084000000002</v>
       </c>
@@ -13126,7 +13125,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="317" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>60.529623000000001</v>
       </c>
@@ -13167,7 +13166,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="318" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>60.528432000000002</v>
       </c>
@@ -13208,7 +13207,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="319" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>60.550871999999998</v>
       </c>
@@ -13249,7 +13248,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="320" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>60.544732000000003</v>
       </c>
@@ -13290,7 +13289,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="321" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>60.544178000000002</v>
       </c>
@@ -13331,7 +13330,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="322" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>60.560132000000003</v>
       </c>
@@ -13369,7 +13368,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="323" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>60.558625999999997</v>
       </c>
@@ -13410,7 +13409,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="324" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>60.559897999999997</v>
       </c>
@@ -13451,7 +13450,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="325" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>60.539445999999998</v>
       </c>
@@ -13492,7 +13491,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="326" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>60.547573</v>
       </c>
@@ -13527,7 +13526,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="327" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>60.541946000000003</v>
       </c>
@@ -13565,7 +13564,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="328" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>60.547286</v>
       </c>
@@ -13606,7 +13605,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="329" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>60.010714</v>
       </c>
@@ -13647,7 +13646,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="330" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>59.889726000000003</v>
       </c>
@@ -13685,7 +13684,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="331" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>60.009824999999999</v>
       </c>
@@ -13723,7 +13722,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="332" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>59.990980999999998</v>
       </c>
@@ -13767,7 +13766,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="333" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>59.889726000000003</v>
       </c>
@@ -13808,7 +13807,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="334" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>59.899141999999998</v>
       </c>
@@ -13852,7 +13851,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="335" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>59.895373999999997</v>
       </c>
@@ -13890,7 +13889,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="336" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>59.796548999999999</v>
       </c>
@@ -13928,7 +13927,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="337" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>59.993304000000002</v>
       </c>
@@ -13972,7 +13971,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="338" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>60.557586999999998</v>
       </c>
@@ -14010,7 +14009,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="339" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>60.775564000000003</v>
       </c>
@@ -14051,7 +14050,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="340" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>59.794373</v>
       </c>
@@ -14092,7 +14091,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="341" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>59.803417000000003</v>
       </c>
@@ -14133,7 +14132,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="342" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>59.800241999999997</v>
       </c>
@@ -14174,7 +14173,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="343" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>59.791307000000003</v>
       </c>
@@ -14215,7 +14214,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="344" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>59.712266999999997</v>
       </c>
@@ -14256,7 +14255,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="345" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>59.903934999999997</v>
       </c>
@@ -14297,7 +14296,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="346" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>60.552858999999998</v>
       </c>
@@ -14332,7 +14331,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="347" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>59.289428999999998</v>
       </c>
@@ -14367,7 +14366,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="348" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>59.289814</v>
       </c>
@@ -14402,7 +14401,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="349" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>59.292901999999998</v>
       </c>
@@ -14437,7 +14436,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="350" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>59.307583000000001</v>
       </c>
@@ -14472,7 +14471,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="351" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>59.302593999999999</v>
       </c>
@@ -14507,7 +14506,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="352" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>59.302142000000003</v>
       </c>
@@ -14539,7 +14538,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="353" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>59.270178999999999</v>
       </c>
@@ -14574,7 +14573,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="354" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>59.255383000000002</v>
       </c>
@@ -14609,7 +14608,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="355" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>61.051636000000002</v>
       </c>
@@ -14644,7 +14643,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="356" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>61.066577000000002</v>
       </c>
@@ -14682,7 +14681,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="357" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>60.708468000000003</v>
       </c>
@@ -14705,7 +14704,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="358" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>60.704098999999999</v>
       </c>
@@ -14731,7 +14730,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="359" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>60.753950000000003</v>
       </c>
@@ -14751,7 +14750,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="360" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>60.753866000000002</v>
       </c>
@@ -14771,7 +14770,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="361" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>59.235382000000001</v>
       </c>
@@ -14803,7 +14802,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="362" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>59.242953999999997</v>
       </c>
@@ -14835,7 +14834,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="363" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>59.260731999999997</v>
       </c>
@@ -14867,7 +14866,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="364" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>59.293725000000002</v>
       </c>
@@ -14893,7 +14892,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="365" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>59.29307</v>
       </c>
@@ -14919,7 +14918,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="366" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>59.292150999999997</v>
       </c>
@@ -14945,7 +14944,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="367" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>59.274639999999998</v>
       </c>
@@ -14971,7 +14970,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="368" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>59.258699999999997</v>
       </c>
@@ -14997,7 +14996,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="369" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>59.260193999999998</v>
       </c>
@@ -15032,7 +15031,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="370" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>59.231777999999998</v>
       </c>
@@ -15061,7 +15060,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="371" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>59.238472999999999</v>
       </c>
@@ -15090,7 +15089,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="372" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>59.248548999999997</v>
       </c>
@@ -15116,7 +15115,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="373" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>59.249270000000003</v>
       </c>
@@ -15142,7 +15141,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="374" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>59.236818999999997</v>
       </c>
@@ -15168,7 +15167,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="375" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>59.294395000000002</v>
       </c>
@@ -15194,7 +15193,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="376" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>60.716999999999999</v>
       </c>
@@ -15220,7 +15219,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="377" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>60.483449999999998</v>
       </c>
@@ -15249,7 +15248,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="378" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>60.455469999999998</v>
       </c>
@@ -15281,7 +15280,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="379" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>60.441290000000002</v>
       </c>
@@ -15313,7 +15312,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="380" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>60.724879999999999</v>
       </c>
@@ -15342,7 +15341,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="381" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>60.736899999999999</v>
       </c>
@@ -15371,7 +15370,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="382" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>60.622169999999997</v>
       </c>
@@ -15400,7 +15399,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="383" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>60.659821999999998</v>
       </c>
@@ -15426,7 +15425,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="384" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>60.659751999999997</v>
       </c>
@@ -15452,7 +15451,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="385" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>60.710090000000001</v>
       </c>
@@ -15478,7 +15477,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="386" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>60.713441000000003</v>
       </c>
@@ -15504,7 +15503,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="387" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>60.730057000000002</v>
       </c>
@@ -15527,7 +15526,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="388" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>60.747804000000002</v>
       </c>
@@ -15553,7 +15552,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="389" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>60.768495000000001</v>
       </c>
@@ -15579,7 +15578,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="390" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>60.760890000000003</v>
       </c>
@@ -15605,7 +15604,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="391" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>60.735120000000002</v>
       </c>
@@ -15631,7 +15630,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="392" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>60.754246000000002</v>
       </c>
@@ -15657,7 +15656,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="393" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>60.089469999999999</v>
       </c>
@@ -15686,7 +15685,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="394" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>60.123438</v>
       </c>
@@ -15715,7 +15714,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="395" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>60.122529999999998</v>
       </c>
@@ -15744,7 +15743,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="396" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>60.144176999999999</v>
       </c>
@@ -15770,7 +15769,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="397" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>60.114669999999997</v>
       </c>
@@ -15796,7 +15795,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="398" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>60.154313000000002</v>
       </c>
@@ -15822,7 +15821,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="399" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>60.153574999999996</v>
       </c>
@@ -15845,7 +15844,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="400" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>60.525143999999997</v>
       </c>
@@ -15868,7 +15867,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="401" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>60.497979999999998</v>
       </c>
@@ -15891,7 +15890,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="402" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>60.558486000000002</v>
       </c>
@@ -15914,7 +15913,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="403" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>60.551000000000002</v>
       </c>
@@ -15937,7 +15936,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="404" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>60.535299999999999</v>
       </c>
@@ -15963,7 +15962,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="405" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>60.537410000000001</v>
       </c>
@@ -15989,7 +15988,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="406" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>60.513100000000001</v>
       </c>
@@ -16015,7 +16014,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="407" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>60.762376000000003</v>
       </c>
@@ -16038,7 +16037,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="408" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>60.523439000000003</v>
       </c>
@@ -16061,7 +16060,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="409" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>60.501480000000001</v>
       </c>
@@ -16090,7 +16089,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="410" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>60.50479</v>
       </c>
@@ -16119,7 +16118,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="411" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>60.509270000000001</v>
       </c>
@@ -16145,7 +16144,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="412" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>60.513469999999998</v>
       </c>
@@ -16174,7 +16173,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="413" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>60.513579999999997</v>
       </c>
@@ -16203,7 +16202,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="414" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>59.994801000000002</v>
       </c>
@@ -16232,7 +16231,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="415" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>59.991247999999999</v>
       </c>
@@ -16261,7 +16260,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="416" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>59.911225000000002</v>
       </c>
@@ -16287,7 +16286,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="417" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>59.709899</v>
       </c>
@@ -16313,7 +16312,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="418" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>59.756639999999997</v>
       </c>
@@ -16342,7 +16341,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="419" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>59.710645</v>
       </c>
@@ -16368,7 +16367,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="420" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>59.713859999999997</v>
       </c>
@@ -16404,26 +16403,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d926a86a-5568-4b7d-bc79-ff57474c3d81" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c712875-1d84-4c30-b685-6583cdc31ab4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009EC30B1665E4E345AD1F5882B3F4E485" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d7bae734f987b76f80c297ae82afdd56">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c712875-1d84-4c30-b685-6583cdc31ab4" xmlns:ns3="d926a86a-5568-4b7d-bc79-ff57474c3d81" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447573c8954a6803590d63b83a14f29b" ns2:_="" ns3:_="">
     <xsd:import namespace="7c712875-1d84-4c30-b685-6583cdc31ab4"/>
@@ -16618,26 +16597,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B43818E5-EF1B-4BEC-B731-33B6460C5D0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d926a86a-5568-4b7d-bc79-ff57474c3d81"/>
-    <ds:schemaRef ds:uri="7c712875-1d84-4c30-b685-6583cdc31ab4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F3AD7C0-3A14-4F65-8B91-88E056C7A99D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d926a86a-5568-4b7d-bc79-ff57474c3d81" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c712875-1d84-4c30-b685-6583cdc31ab4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD980A78-2707-48B3-92AD-C4B5EF11B82D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16654,4 +16634,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F3AD7C0-3A14-4F65-8B91-88E056C7A99D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B43818E5-EF1B-4BEC-B731-33B6460C5D0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d926a86a-5568-4b7d-bc79-ff57474c3d81"/>
+    <ds:schemaRef ds:uri="7c712875-1d84-4c30-b685-6583cdc31ab4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>